--- a/data/trans_dic/P19E_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19E_R-Estudios-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se cepilla los dientes una o ninguna vez al día</t>
+          <t>Población que se cepilla los dientes una o ninguna vez al día (tasa de respuesta: 98,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>48,82; 56,07</t>
+          <t>48,82; 55,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,2; 52,54</t>
+          <t>44,58; 52,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,82; 43,67</t>
+          <t>37,19; 43,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,18; 38,56</t>
+          <t>32,98; 38,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,08; 48,07</t>
+          <t>43,05; 48,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,44; 43,25</t>
+          <t>38,66; 43,55</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,22; 34,49</t>
+          <t>30,27; 34,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,75; 24,08</t>
+          <t>13,35; 24,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,96; 21,69</t>
+          <t>18,11; 21,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,19; 13,19</t>
+          <t>8,23; 13,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,65; 27,6</t>
+          <t>24,86; 27,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,65; 17,97</t>
+          <t>12,54; 18,17</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,78; 24,07</t>
+          <t>16,64; 24,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,92; 20,57</t>
+          <t>13,16; 20,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,97; 13,26</t>
+          <t>7,94; 13,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 8,96</t>
+          <t>5,73; 8,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,04; 17,55</t>
+          <t>13,05; 17,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,88; 14,02</t>
+          <t>9,79; 14,05</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,05; 36,5</t>
+          <t>32,98; 36,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,72; 26,7</t>
+          <t>18,72; 26,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,55; 25,51</t>
+          <t>22,45; 25,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,79; 17,07</t>
+          <t>12,77; 17,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,12; 30,32</t>
+          <t>28,06; 30,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,69; 21,09</t>
+          <t>17,12; 21,18</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se cepilla los dientes una o ninguna vez al día</t>
+          <t>Población que se cepilla los dientes una o ninguna vez al día (tasa de respuesta: 98,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>348335; 400095</t>
+          <t>348327; 399247</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>224148; 266457</t>
+          <t>226091; 267401</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>350242; 415376</t>
+          <t>353743; 415812</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>245127; 284873</t>
+          <t>243606; 283746</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>717181; 800213</t>
+          <t>716774; 799118</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>478939; 538864</t>
+          <t>481673; 542550</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>613073; 699580</t>
+          <t>614002; 701013</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>336899; 549993</t>
+          <t>305089; 549946</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>349814; 422524</t>
+          <t>352806; 422980</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>183075; 294703</t>
+          <t>183826; 297827</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>980184; 1097302</t>
+          <t>988586; 1099452</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>571644; 812091</t>
+          <t>566751; 821044</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>90517; 129838</t>
+          <t>89722; 131408</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>83419; 132868</t>
+          <t>85031; 133554</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43358; 72178</t>
+          <t>43213; 72509</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37278; 59139</t>
+          <t>37826; 58369</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>141256; 190126</t>
+          <t>141414; 190521</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>129046; 183097</t>
+          <t>127793; 183476</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1084383; 1197717</t>
+          <t>1082046; 1197711</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>643590; 917660</t>
+          <t>643638; 911266</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>776560; 878521</t>
+          <t>772844; 878299</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>464526; 620049</t>
+          <t>463822; 619591</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1890636; 2038635</t>
+          <t>1886924; 2033265</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1180204; 1491340</t>
+          <t>1210760; 1497369</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19E_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19E_R-Estudios-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>48,82; 55,95</t>
+          <t>49,12; 56,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44,58; 52,73</t>
+          <t>43,26; 51,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,19; 43,71</t>
+          <t>36,85; 43,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32,98; 38,41</t>
+          <t>32,67; 38,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,05; 48,0</t>
+          <t>42,99; 48,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,66; 43,55</t>
+          <t>38,07; 42,52</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,27; 34,56</t>
+          <t>30,45; 34,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,35; 24,07</t>
+          <t>21,11; 24,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,11; 21,72</t>
+          <t>18,13; 22,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,23; 13,33</t>
+          <t>11,67; 14,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,86; 27,65</t>
+          <t>24,86; 27,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,54; 18,17</t>
+          <t>16,93; 19,2</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,64; 24,37</t>
+          <t>16,67; 24,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,16; 20,68</t>
+          <t>11,83; 17,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,94; 13,32</t>
+          <t>8,26; 13,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 8,85</t>
+          <t>6,07; 9,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,05; 17,58</t>
+          <t>13,33; 17,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,79; 14,05</t>
+          <t>9,36; 12,83</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,98; 36,5</t>
+          <t>33,04; 36,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,72; 26,51</t>
+          <t>23,67; 26,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22,45; 25,51</t>
+          <t>22,51; 25,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,77; 17,05</t>
+          <t>15,78; 17,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,06; 30,24</t>
+          <t>28,04; 30,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,12; 21,18</t>
+          <t>19,99; 21,79</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>246523</t>
+          <t>270573</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>264307</t>
+          <t>283323</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>510830</t>
+          <t>553896</t>
         </is>
       </c>
     </row>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>348327; 399247</t>
+          <t>350514; 402641</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>226091; 267401</t>
+          <t>246476; 293290</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>353743; 415812</t>
+          <t>350516; 411944</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>243606; 283746</t>
+          <t>263046; 305952</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>716774; 799118</t>
+          <t>715644; 799208</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>481673; 542550</t>
+          <t>523433; 584608</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>476027</t>
+          <t>511404</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>252392</t>
+          <t>281624</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>728420</t>
+          <t>793028</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>614002; 701013</t>
+          <t>617582; 705042</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>305089; 549946</t>
+          <t>469102; 553389</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>352806; 422980</t>
+          <t>353174; 428416</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>183826; 297827</t>
+          <t>252977; 311234</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>988586; 1099452</t>
+          <t>988519; 1102437</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>566751; 821044</t>
+          <t>743095; 842576</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>103983</t>
+          <t>102822</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47362</t>
+          <t>55600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>151344</t>
+          <t>158422</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>89722; 131408</t>
+          <t>89896; 132520</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>85031; 133554</t>
+          <t>84123; 126891</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43213; 72509</t>
+          <t>44949; 73618</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>37826; 58369</t>
+          <t>44600; 71525</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>141414; 190521</t>
+          <t>144442; 194512</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>127793; 183476</t>
+          <t>135205; 185432</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>826533</t>
+          <t>884798</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>564061</t>
+          <t>620547</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1390594</t>
+          <t>1505345</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1082046; 1197711</t>
+          <t>1083991; 1198244</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>643638; 911266</t>
+          <t>829014; 940565</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>772844; 878299</t>
+          <t>774997; 876724</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>463822; 619591</t>
+          <t>584801; 661377</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1886924; 2033265</t>
+          <t>1885413; 2034227</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1210760; 1497369</t>
+          <t>1441377; 1570611</t>
         </is>
       </c>
     </row>
